--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -136,28 +136,28 @@
     <t>21:35</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Juventude</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
     <t>Remo</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Criciúma</t>
   </si>
   <si>
     <t>Avaí</t>
@@ -684,76 +684,76 @@
         <v>49</v>
       </c>
       <c r="L2">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="M2">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="N2">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P2">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="S2">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="T2">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="U2">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="V2">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Z2">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AA2">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC2">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AD2">
-        <v>4.5</v>
+        <v>5.95</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AG2">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AH2">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="AI2">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="s">
         <v>50</v>
@@ -800,70 +800,70 @@
         <v>49</v>
       </c>
       <c r="L3">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="M3">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="N3">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P3">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T3">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="U3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="V3">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="W3">
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y3">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Z3">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AA3">
+        <v>2.45</v>
+      </c>
+      <c r="AB3">
         <v>2.2</v>
       </c>
-      <c r="AB3">
-        <v>2.75</v>
-      </c>
       <c r="AC3">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AD3">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH3">
         <v>12</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
         <v>42</v>
@@ -934,28 +934,28 @@
         <v>2.15</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V4">
-        <v>8.75</v>
+        <v>8.9</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z4">
         <v>1.42</v>
@@ -970,22 +970,22 @@
         <v>1.53</v>
       </c>
       <c r="AD4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE4">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH4">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="AI4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -136,28 +136,28 @@
     <t>21:35</t>
   </si>
   <si>
+    <t>Brazil Serie A</t>
+  </si>
+  <si>
     <t>Brazil Serie B</t>
   </si>
   <si>
-    <t>Brazil Serie A</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
+    <t>Juventude</t>
+  </si>
+  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
-    <t>Juventude</t>
-  </si>
-  <si>
     <t>Remo</t>
   </si>
   <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
     <t>Criciúma</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
   </si>
   <si>
     <t>Avaí</t>
@@ -684,76 +684,76 @@
         <v>49</v>
       </c>
       <c r="L2">
-        <v>2.53</v>
+        <v>3.54</v>
       </c>
       <c r="M2">
-        <v>2.72</v>
+        <v>3.09</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P2">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q2">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="T2">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="U2">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="V2">
-        <v>12</v>
+        <v>8.9</v>
       </c>
       <c r="W2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y2">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="Z2">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="AB2">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="AC2">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AD2">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG2">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH2">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AJ2" t="s">
         <v>50</v>
@@ -800,76 +800,76 @@
         <v>49</v>
       </c>
       <c r="L3">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="M3">
+        <v>2.92</v>
+      </c>
+      <c r="N3">
         <v>2.95</v>
       </c>
-      <c r="N3">
-        <v>2.39</v>
-      </c>
       <c r="O3">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P3">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q3">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T3">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="U3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V3">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y3">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="Z3">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AA3">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AB3">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC3">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AD3">
-        <v>4.75</v>
+        <v>5.95</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG3">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="s">
         <v>50</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>42</v>
@@ -916,13 +916,13 @@
         <v>49</v>
       </c>
       <c r="L4">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M4">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N4">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="O4">
         <v>1.93</v>
@@ -934,58 +934,58 @@
         <v>2.15</v>
       </c>
       <c r="R4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T4">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V4">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W4">
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y4">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="Z4">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AA4">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AB4">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AC4">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AD4">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AE4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AG4">
         <v>1.75</v>
       </c>
       <c r="AH4">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -136,28 +136,28 @@
     <t>21:35</t>
   </si>
   <si>
+    <t>Brazil Serie B</t>
+  </si>
+  <si>
     <t>Brazil Serie A</t>
   </si>
   <si>
-    <t>Brazil Serie B</t>
-  </si>
-  <si>
     <t>2025</t>
   </si>
   <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
     <t>Juventude</t>
   </si>
   <si>
-    <t>Botafogo SP</t>
-  </si>
-  <si>
     <t>Remo</t>
   </si>
   <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
     <t>São Paulo</t>
-  </si>
-  <si>
-    <t>Criciúma</t>
   </si>
   <si>
     <t>Avaí</t>
@@ -684,76 +684,76 @@
         <v>49</v>
       </c>
       <c r="L2">
-        <v>3.54</v>
+        <v>2.53</v>
       </c>
       <c r="M2">
-        <v>3.09</v>
+        <v>2.72</v>
       </c>
       <c r="N2">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P2">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S2">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T2">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="U2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V2">
-        <v>8.9</v>
+        <v>12</v>
       </c>
       <c r="W2">
         <v>1.02</v>
       </c>
       <c r="X2">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y2">
-        <v>6.25</v>
+        <v>5.5</v>
       </c>
       <c r="Z2">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA2">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="AC2">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AD2">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AE2">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AG2">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH2">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AI2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AJ2" t="s">
         <v>50</v>
@@ -800,76 +800,76 @@
         <v>49</v>
       </c>
       <c r="L3">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="M3">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="N3">
-        <v>2.95</v>
+        <v>2.39</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P3">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S3">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T3">
-        <v>3.94</v>
+        <v>3.45</v>
       </c>
       <c r="U3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V3">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>5.97</v>
+        <v>6.5</v>
       </c>
       <c r="Z3">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AA3">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AB3">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AC3">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AD3">
-        <v>5.95</v>
+        <v>5</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AG3">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH3">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="s">
         <v>50</v>
@@ -889,7 +889,7 @@
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
         <v>42</v>
@@ -916,13 +916,13 @@
         <v>49</v>
       </c>
       <c r="L4">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M4">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N4">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="O4">
         <v>1.93</v>
@@ -937,16 +937,16 @@
         <v>1.44</v>
       </c>
       <c r="S4">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T4">
         <v>3.3</v>
       </c>
       <c r="U4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="V4">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W4">
         <v>1.04</v>
@@ -955,31 +955,31 @@
         <v>1.09</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA4">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AB4">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AC4">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AD4">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AE4">
         <v>1.17</v>
       </c>
       <c r="AF4">
-        <v>2.17</v>
+        <v>2.01</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH4">
         <v>9.300000000000001</v>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.53</v>
+        <v>3.25</v>
       </c>
       <c r="M2" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.3</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.18</v>
-      </c>
       <c r="T2" t="n">
-        <v>3.98</v>
+        <v>3.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
         <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AH3" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.93</v>
@@ -968,7 +968,7 @@
         <v>1.29</v>
       </c>
       <c r="V4" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -977,25 +977,25 @@
         <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA4" t="n">
         <v>2.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
         <v>2</v>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
         <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y2" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD2" t="n">
         <v>6</v>
       </c>
-      <c r="Z2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>5</v>
-      </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O3" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2</v>
-      </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S3" t="n">
         <v>2.3</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.1</v>
-      </c>
       <c r="T3" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
         <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AH3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="N2" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
         <v>2</v>
@@ -692,58 +692,58 @@
         <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="U2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.75</v>
+        <v>6.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
         <v>2.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -806,13 +806,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="O3" t="n">
         <v>2.5</v>
@@ -827,40 +827,40 @@
         <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
         <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>6.81</v>
       </c>
       <c r="Z3" t="n">
         <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AE3" t="n">
         <v>1.15</v>
@@ -869,13 +869,13 @@
         <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
         <v>10</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
         <v>1.93</v>
@@ -956,7 +956,7 @@
         <v>2.15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
         <v>2.3</v>
@@ -971,25 +971,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AA4" t="n">
         <v>2.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AD4" t="n">
         <v>4.8</v>
@@ -998,16 +998,16 @@
         <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH4" t="n">
         <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -692,28 +692,28 @@
         <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
         <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.4</v>
+        <v>5.48</v>
       </c>
       <c r="Z2" t="n">
         <v>1.53</v>
@@ -728,10 +728,10 @@
         <v>1.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AF2" t="n">
         <v>2.32</v>
@@ -830,28 +830,28 @@
         <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="W3" t="n">
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.81</v>
+        <v>6</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AB3" t="n">
         <v>2.38</v>
@@ -869,10 +869,10 @@
         <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AI3" t="n">
         <v>1.04</v>
@@ -959,25 +959,25 @@
         <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
         <v>1.42</v>
@@ -992,22 +992,22 @@
         <v>1.53</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="M2" t="n">
-        <v>2.72</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U2" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="V2" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>2.72</v>
       </c>
       <c r="N3" t="n">
-        <v>2.39</v>
+        <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.55</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="N2" t="n">
-        <v>2.39</v>
+        <v>2.72</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,73 +806,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.53</v>
+        <v>4.6</v>
       </c>
       <c r="M3" t="n">
-        <v>2.72</v>
+        <v>3.28</v>
       </c>
       <c r="N3" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
         <v>2.3</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.48</v>
+        <v>7.11</v>
       </c>
       <c r="Z3" t="n">
         <v>1.53</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
         <v>2.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AH3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AI3" t="n">
         <v>1.01</v>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N4" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.93</v>
@@ -959,55 +959,55 @@
         <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
         <v>8.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.61</v>
+        <v>4.6</v>
       </c>
       <c r="M2" t="n">
-        <v>2.87</v>
+        <v>3.28</v>
       </c>
       <c r="N2" t="n">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S2" t="n">
         <v>2.3</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.16</v>
-      </c>
       <c r="T2" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.25</v>
+        <v>7.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.35</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>4.6</v>
+        <v>2.61</v>
       </c>
       <c r="M3" t="n">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="N3" t="n">
-        <v>1.91</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.11</v>
+        <v>6.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>6.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -674,76 +674,76 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.6</v>
+        <v>2.95</v>
       </c>
       <c r="M2" t="n">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="N2" t="n">
-        <v>1.91</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.11</v>
+        <v>5.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>6.05</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AH2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -806,76 +806,76 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.61</v>
+        <v>3.75</v>
       </c>
       <c r="M3" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.35</v>
+        <v>4.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>9.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.93</v>
@@ -956,10 +956,10 @@
         <v>2.15</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="T4" t="n">
         <v>3.6</v>
@@ -968,46 +968,46 @@
         <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH4" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,19 +648,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -670,80 +670,80 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="M2" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.05</v>
+        <v>4.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AL2" s="3" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,102 +780,102 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AH3" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '56']</t>
         </is>
       </c>
       <c r="AL3" s="3" t="n">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="O4" t="n">
         <v>1.93</v>
@@ -986,10 +986,10 @@
         <v>2.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AD4" t="n">
         <v>5.5</v>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL4"/>
+  <dimension ref="A1:AK5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,85 +543,80 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>awayGoals</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -638,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -648,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -674,88 +669,85 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="N2" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>6.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
-        <v>1.06</v>
+        <v>2.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.54</v>
+        <v>6.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.45</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['6', '56']</t>
+        </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AH2" t="n">
-        <v>9.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>45862.79166666666</v>
       </c>
     </row>
@@ -770,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -780,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -806,88 +798,85 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="M3" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>10</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.54</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>2.54</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.5</v>
+        <v>2.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['85']</t>
+        </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>['6', '56']</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>45862.79166666666</v>
       </c>
     </row>
@@ -897,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -912,114 +901,240 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>45862.875</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>45862</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>2.35</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5" t="n">
         <v>2.9</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N5" t="n">
         <v>2.87</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['29', '45+2']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.93</v>
       </c>
-      <c r="P4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="AJ5" t="n">
         <v>2.15</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AK5" s="3" t="n">
         <v>45862.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-07-24.xlsx
+++ b/jogos_2025-07-24.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="M2" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>1.95</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.45</v>
+        <v>2.61</v>
       </c>
       <c r="R2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.05</v>
+        <v>4.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -732,20 +732,20 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['6', '56']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45862.79166666666</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.61</v>
+        <v>3.45</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="X3" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.2</v>
+        <v>6.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -861,20 +861,20 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['6', '56']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45862.79166666666</v>
